--- a/data/codebook/Q10.xlsx
+++ b/data/codebook/Q10.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="158">
   <si>
     <t>RQ1</t>
   </si>
@@ -38,6 +38,9 @@
   </si>
   <si>
     <t>PERCEPÇÕES, REFLEXÕES E AVALIAÇÕES SOBRE ER</t>
+  </si>
+  <si>
+    <t>Avaliação positiva e reconhecimento da importância</t>
   </si>
   <si>
     <t>Yes, it was a great experience, although complicated.</t>
@@ -68,6 +71,9 @@
     <t>PARTICIPAÇÃO ATIVA E ABRANGENTE EM ENGENHARIA DE REQUISITOS</t>
   </si>
   <si>
+    <t>Definição-análise-documentação ativa</t>
+  </si>
+  <si>
     <t>I've been working on a project for two years</t>
   </si>
   <si>
@@ -93,6 +99,9 @@
     <t>P4</t>
   </si>
   <si>
+    <t>Todas as fases do ciclo</t>
+  </si>
+  <si>
     <t>I have participated in all phases of a data science project lifecycle.</t>
   </si>
   <si>
@@ -108,6 +117,9 @@
     <t>PARTICIPAÇÃO PARCIAL OU PERIFÉRICA</t>
   </si>
   <si>
+    <t>Descrição contextual do projeto sem detalhamento de RE:</t>
+  </si>
+  <si>
     <t>I have participated in projects</t>
   </si>
   <si>
@@ -136,6 +148,9 @@
     <t>TÉCNICAS E ARTEFATOS DE ENGENHARIA DE REQUISITOS</t>
   </si>
   <si>
+    <t>Documentação formal e especificações</t>
+  </si>
+  <si>
     <t>Formal documentation of requirements in detailed documents, which may include functional and non-functional specifications, and use cases.</t>
   </si>
   <si>
@@ -170,6 +185,9 @@
     <t>P10</t>
   </si>
   <si>
+    <t>Técnicas de elicitação (entrevistas, workshops, análise documental)</t>
+  </si>
+  <si>
     <t>Yes</t>
   </si>
   <si>
@@ -229,6 +247,9 @@
     <t>P13</t>
   </si>
   <si>
+    <t>Documentação restrita a aspectos técnicos pontuais</t>
+  </si>
+  <si>
     <t>In this case, my experience in this area is more focused on code documentation and creating pipeline diagrams. I have participated in some audits conducted by the requirements team, but I don't consider myself experienced in that field.</t>
   </si>
   <si>
@@ -241,6 +262,9 @@
     <t>P15</t>
   </si>
   <si>
+    <t>Refinamento e processos iterativos com cliente</t>
+  </si>
+  <si>
     <t>Yes, I have participated in requirements refinement processes</t>
   </si>
   <si>
@@ -266,6 +290,9 @@
     <t>P16</t>
   </si>
   <si>
+    <t>Análise de processos de negócio e domínio</t>
+  </si>
+  <si>
     <t>Yes, I participate, and the analysis and design of the business processes involved in the change resolved by the project takes place within the scope of this work.</t>
   </si>
   <si>
@@ -278,9 +305,15 @@
     <t>P18</t>
   </si>
   <si>
+    <t>Resposta afirmativa monossilábica sem detalhamento</t>
+  </si>
+  <si>
     <t>P19</t>
   </si>
   <si>
+    <t>Reflexão crítica sobre limitações práticas</t>
+  </si>
+  <si>
     <t>I have participated in several definitions, analyses, and brief documentation, but the terms have always been extremely short for conducting an in-depth study</t>
   </si>
   <si>
@@ -354,6 +387,9 @@
     <t>P25</t>
   </si>
   <si>
+    <t>Participação consistente e de longa data</t>
+  </si>
+  <si>
     <t>I've worked on, sometimes with less interaction</t>
   </si>
   <si>
@@ -412,6 +448,9 @@
     <t>P27</t>
   </si>
   <si>
+    <t>Elicitação informal sem artefatos formais</t>
+  </si>
+  <si>
     <t>I participated in the requirements elicitation for a software module that would retrieve and process data from a data warehouse</t>
   </si>
   <si>
@@ -437,6 +476,9 @@
     <t>P28</t>
   </si>
   <si>
+    <t>Prototipação e jornadas de usuário</t>
+  </si>
+  <si>
     <t>I participated in several user journeys, talking to customers to understand how an AI product could help in the daily lives of the target audience.</t>
   </si>
   <si>
@@ -496,6 +538,9 @@
     <t>P32</t>
   </si>
   <si>
+    <t>Metodologias ágeis e gestão de tarefas</t>
+  </si>
+  <si>
     <t>I always participate</t>
   </si>
   <si>
@@ -521,12 +566,18 @@
     <t>P33</t>
   </si>
   <si>
+    <t>Avaliação ambivalente (custo-benefício)</t>
+  </si>
+  <si>
     <t>I don't usually participate much in the requirements engineering phase.</t>
   </si>
   <si>
     <t>P34</t>
   </si>
   <si>
+    <t>Elicitação informal sem documentação formal</t>
+  </si>
+  <si>
     <t>In some projects, yes</t>
   </si>
   <si>
@@ -564,6 +615,9 @@
     <t>P37</t>
   </si>
   <si>
+    <t>Não-foco ou baixa participação</t>
+  </si>
+  <si>
     <t>I usually do not focus on Req.</t>
   </si>
   <si>
@@ -607,6 +661,9 @@
     <t>P41</t>
   </si>
   <si>
+    <t>Adaptação dinâmica a mudanças</t>
+  </si>
+  <si>
     <t>defining, adjusting requirements along with the changes in the understanding of the project, new requirements from stakeholders, impossibility to fulfill some requirements in accordance with technology state</t>
   </si>
   <si>
@@ -619,6 +676,9 @@
     <t>P43</t>
   </si>
   <si>
+    <t>Liderança técnica e coordenação com stakeholders</t>
+  </si>
+  <si>
     <t xml:space="preserve">As a product owner I often participate in workshops, interviews to gather requirements with business analysts and other stakeholders  </t>
   </si>
   <si>
@@ -673,6 +733,9 @@
     <t>P49</t>
   </si>
   <si>
+    <t>Briefing leve (lightweight)</t>
+  </si>
+  <si>
     <t>i wrote lightweight requirements briefling touching on behaviour (including constraints), features</t>
   </si>
   <si>
@@ -710,14 +773,16 @@
     <t>P53</t>
   </si>
   <si>
-    <t xml:space="preserve">Experiência limitada a contexto acadêmico/pessoal
-</t>
+    <t>Usuário de documentação, não definidor</t>
   </si>
   <si>
     <t>My involvement in the field of ER Always has been limited to methodological assumptions, acting more as a user of requirements documentation than someone actively involved in defining them (except for specific cases where my intervention was necessary to correct an error in the documentation or to conclude that a requirement was unfeasible for a project).</t>
   </si>
   <si>
     <t>P54</t>
+  </si>
+  <si>
+    <t>Quotes que indicam pouca participação ou que RE não é o foco do trabalho</t>
   </si>
   <si>
     <t>I've only made very small personal projects so i basically did little to no requirements engineering.</t>
@@ -770,15 +835,15 @@
     </font>
     <font/>
     <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <sz val="9.0"/>
       <color theme="1"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -934,7 +999,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -943,7 +1008,10 @@
     </xf>
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -951,23 +1019,23 @@
     <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="9" fillId="0" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="10" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="10" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="10" fillId="5" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="6" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="10" fillId="6" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="7" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="10" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="8" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="10" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
@@ -1201,916 +1269,1055 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="3"/>
+      <c r="G1" s="4"/>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="4"/>
     </row>
     <row r="3">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="8"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="9"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="4"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="14" t="s">
+      <c r="F4" s="15" t="s">
         <v>7</v>
       </c>
+      <c r="G4" s="4"/>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15" t="s">
+      <c r="B5" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="C5" s="4"/>
+      <c r="D5" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="4"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="4"/>
+      <c r="D6" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="4"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="15" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6" s="15" t="s">
+      <c r="C7" s="4"/>
+      <c r="D7" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="4"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="4"/>
+      <c r="D8" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G8" s="4"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="4"/>
+      <c r="D9" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="4"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15" t="s">
+      <c r="B10" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="C10" s="4"/>
+      <c r="D10" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" s="4"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="C11" s="4"/>
+      <c r="D11" s="16" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="15" t="s">
+      <c r="E11" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="4"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="4"/>
+      <c r="D12" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="G12" s="4"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="4"/>
+      <c r="D13" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" s="4"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="C14" s="4"/>
+      <c r="D14" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G14" s="4"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="4"/>
+      <c r="D15" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G15" s="4"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="4"/>
+      <c r="D16" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="G16" s="4"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15" t="s">
+      <c r="B17" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="4"/>
+      <c r="D17" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" s="4"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="4"/>
+      <c r="D18" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="G18" s="4"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="G19" s="4"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G20" s="4"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C21" s="4"/>
+      <c r="D21" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G21" s="4"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="4"/>
+      <c r="D22" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="G22" s="4"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C23" s="4"/>
+      <c r="D23" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23" s="4"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="4"/>
+      <c r="D24" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G24" s="4"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="C25" s="4"/>
+      <c r="D25" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="G25" s="4"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="4"/>
+      <c r="D26" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="G26" s="4"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" s="4"/>
+      <c r="D27" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>76</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="4"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C28" s="4"/>
+      <c r="D28" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G28" s="4"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="B29" s="16" t="s">
+        <v>79</v>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G29" s="4"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="E30" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G30" s="4"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C31" s="4"/>
+      <c r="D31" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="G31" s="4"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" s="4"/>
+      <c r="D32" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="E32" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="G32" s="4"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="4"/>
+      <c r="D33" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F33" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G33" s="4"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C34" s="4"/>
+      <c r="D34" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="E34" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="G34" s="4"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C35" s="4"/>
+      <c r="D35" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E35" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="G35" s="4"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>100</v>
+      </c>
+      <c r="C36" s="4"/>
+      <c r="D36" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="G36" s="4"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C37" s="4"/>
+      <c r="D37" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="E37" s="17" t="s">
+        <v>105</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G37" s="4"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="C38" s="4"/>
+      <c r="D38" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="E38" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="G38" s="4"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C39" s="4"/>
+      <c r="D39" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E39" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G39" s="4"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C40" s="4"/>
+      <c r="D40" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="E40" s="17" t="s">
+        <v>113</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="G40" s="4"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C41" s="4"/>
+      <c r="D41" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="E41" s="17" t="s">
+        <v>116</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G41" s="4"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C42" s="4"/>
+      <c r="D42" s="16" t="s">
+        <v>118</v>
+      </c>
+      <c r="E42" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="F42" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="G42" s="4"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C43" s="4"/>
+      <c r="D43" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="E43" s="17" t="s">
+        <v>121</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="G43" s="4"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C44" s="4"/>
+      <c r="D44" s="16" t="s">
+        <v>123</v>
+      </c>
+      <c r="E44" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="F44" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G44" s="4"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>125</v>
+      </c>
+      <c r="C45" s="4"/>
+      <c r="D45" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="E45" s="17" t="s">
+        <v>126</v>
+      </c>
+      <c r="F45" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G45" s="4"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C46" s="4"/>
+      <c r="D46" s="16" t="s">
+        <v>128</v>
+      </c>
+      <c r="E46" s="17" t="s">
+        <v>128</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="G46" s="4"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C47" s="4"/>
+      <c r="D47" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="E47" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="G47" s="4"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B48" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="F8" s="15" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="15" t="s">
+      <c r="C48" s="4"/>
+      <c r="D48" s="16" t="s">
+        <v>133</v>
+      </c>
+      <c r="E48" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="G48" s="4"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C49" s="4"/>
+      <c r="D49" s="16" t="s">
+        <v>136</v>
+      </c>
+      <c r="E49" s="17" t="s">
+        <v>136</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G49" s="4"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="15" t="s">
+      <c r="B50" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C50" s="4"/>
+      <c r="D50" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="E50" s="17" t="s">
+        <v>14</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G50" s="4"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="C51" s="4"/>
+      <c r="D51" s="16" t="s">
+        <v>139</v>
+      </c>
+      <c r="E51" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G51" s="4"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="C52" s="4"/>
+      <c r="D52" s="16" t="s">
+        <v>142</v>
+      </c>
+      <c r="E52" s="17" t="s">
+        <v>142</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="G52" s="4"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C53" s="4"/>
+      <c r="D53" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="E53" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G53" s="4"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="C54" s="4"/>
+      <c r="D54" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="E54" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="F54" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G54" s="4"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>149</v>
+      </c>
+      <c r="C55" s="4"/>
+      <c r="D55" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="E55" s="17" t="s">
+        <v>150</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="G55" s="4"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="E12" s="17" t="s">
-        <v>27</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B14" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15" t="s">
+      <c r="B56" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="C56" s="4"/>
+      <c r="D56" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="E56" s="17" t="s">
+        <v>153</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G56" s="4"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" s="15" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="E15" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15" t="s">
-        <v>42</v>
-      </c>
-      <c r="E17" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="E18" s="16" t="s">
-        <v>45</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>47</v>
-      </c>
-      <c r="F19" s="15" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="F23" s="15" t="s">
+      <c r="B57" s="16" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B25" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="E25" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="F25" s="15" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="E26" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15" t="s">
-        <v>64</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="F27" s="15" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B28" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="E29" s="17" t="s">
-        <v>69</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="E30" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="F30" s="15" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="E31" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>77</v>
-      </c>
-      <c r="F32" s="15" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="E33" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="F33" s="15" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="E34" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="F34" s="15" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B35" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E35" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F35" s="15" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="E36" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="F36" s="15" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B37" s="15"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="E37" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="F37" s="15" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="E38" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="F38" s="15" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B39" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="E39" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="F39" s="15" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B40" s="15"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15" t="s">
-        <v>96</v>
-      </c>
-      <c r="E40" s="16" t="s">
-        <v>96</v>
-      </c>
-      <c r="F40" s="15" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15" t="s">
-        <v>98</v>
-      </c>
-      <c r="E41" s="16" t="s">
-        <v>98</v>
-      </c>
-      <c r="F41" s="15" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="15" t="s">
-        <v>100</v>
-      </c>
-      <c r="E42" s="17" t="s">
-        <v>101</v>
-      </c>
-      <c r="F42" s="15" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="15"/>
-      <c r="B43" s="15"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="15" t="s">
-        <v>103</v>
-      </c>
-      <c r="E43" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="F43" s="15" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B44" s="15"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="15" t="s">
-        <v>105</v>
-      </c>
-      <c r="E44" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="F44" s="15" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="B45" s="15"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="15" t="s">
-        <v>107</v>
-      </c>
-      <c r="E45" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="F45" s="15" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B46" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C46" s="15"/>
-      <c r="D46" s="15" t="s">
-        <v>109</v>
-      </c>
-      <c r="E46" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="F46" s="15" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B47" s="15"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="E47" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="F47" s="15" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B48" s="15"/>
-      <c r="C48" s="15"/>
-      <c r="D48" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="E48" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="F48" s="15" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="15"/>
-      <c r="B49" s="15"/>
-      <c r="C49" s="15"/>
-      <c r="D49" s="15" t="s">
-        <v>116</v>
-      </c>
-      <c r="E49" s="16" t="s">
-        <v>116</v>
-      </c>
-      <c r="F49" s="15" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B50" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C50" s="15"/>
-      <c r="D50" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E50" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="F50" s="15" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B51" s="15"/>
-      <c r="C51" s="15"/>
-      <c r="D51" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="E51" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="F51" s="15" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B52" s="15"/>
-      <c r="C52" s="15"/>
-      <c r="D52" s="15" t="s">
-        <v>121</v>
-      </c>
-      <c r="E52" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="F52" s="15" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B53" s="15"/>
-      <c r="C53" s="15"/>
-      <c r="D53" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="E53" s="16" t="s">
-        <v>123</v>
-      </c>
-      <c r="F53" s="15" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="B54" s="15"/>
-      <c r="C54" s="15"/>
-      <c r="D54" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="E54" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="F54" s="15" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="B55" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="C55" s="15"/>
-      <c r="D55" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="E55" s="16" t="s">
-        <v>129</v>
-      </c>
-      <c r="F55" s="15" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="B56" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="C56" s="15"/>
-      <c r="D56" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="E56" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="F56" s="15" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="B57" s="15"/>
-      <c r="C57" s="15"/>
-      <c r="D57" s="15" t="s">
-        <v>133</v>
-      </c>
-      <c r="E57" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="F57" s="15" t="s">
-        <v>135</v>
-      </c>
+      <c r="C57" s="4"/>
+      <c r="D57" s="16" t="s">
+        <v>155</v>
+      </c>
+      <c r="E57" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G57" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">
